--- a/artfynd/A 10274-2024 artfynd.xlsx
+++ b/artfynd/A 10274-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118897056</v>
+        <v>118897464</v>
       </c>
       <c r="B2" t="n">
-        <v>91773</v>
+        <v>90749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727904</v>
+        <v>727878</v>
       </c>
       <c r="R2" t="n">
-        <v>7217822</v>
+        <v>7217756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118899277</v>
+        <v>118897773</v>
       </c>
       <c r="B3" t="n">
-        <v>90009</v>
+        <v>91252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728134</v>
+        <v>727890</v>
       </c>
       <c r="R3" t="n">
-        <v>7217984</v>
+        <v>7217789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118897464</v>
+        <v>118899277</v>
       </c>
       <c r="B4" t="n">
-        <v>90749</v>
+        <v>90009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>256703</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727878</v>
+        <v>728134</v>
       </c>
       <c r="R4" t="n">
-        <v>7217756</v>
+        <v>7217984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118897773</v>
+        <v>118899285</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>90772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1958</v>
+        <v>71</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727890</v>
+        <v>728146</v>
       </c>
       <c r="R5" t="n">
-        <v>7217789</v>
+        <v>7217994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118899285</v>
+        <v>118897056</v>
       </c>
       <c r="B6" t="n">
-        <v>90772</v>
+        <v>91773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728146</v>
+        <v>727904</v>
       </c>
       <c r="R6" t="n">
-        <v>7217994</v>
+        <v>7217822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 10274-2024 artfynd.xlsx
+++ b/artfynd/A 10274-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118897464</v>
+        <v>118899285</v>
       </c>
       <c r="B2" t="n">
-        <v>90749</v>
+        <v>90779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727878</v>
+        <v>728146</v>
       </c>
       <c r="R2" t="n">
-        <v>7217756</v>
+        <v>7217994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118897773</v>
+        <v>118897056</v>
       </c>
       <c r="B3" t="n">
-        <v>91252</v>
+        <v>91780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727890</v>
+        <v>727904</v>
       </c>
       <c r="R3" t="n">
-        <v>7217789</v>
+        <v>7217822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118899277</v>
+        <v>118897773</v>
       </c>
       <c r="B4" t="n">
-        <v>90009</v>
+        <v>91259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>728134</v>
+        <v>727890</v>
       </c>
       <c r="R4" t="n">
-        <v>7217984</v>
+        <v>7217789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118899285</v>
+        <v>118897464</v>
       </c>
       <c r="B5" t="n">
-        <v>90772</v>
+        <v>90756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728146</v>
+        <v>727878</v>
       </c>
       <c r="R5" t="n">
-        <v>7217994</v>
+        <v>7217756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118897056</v>
+        <v>118899277</v>
       </c>
       <c r="B6" t="n">
-        <v>91773</v>
+        <v>90016</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727904</v>
+        <v>728134</v>
       </c>
       <c r="R6" t="n">
-        <v>7217822</v>
+        <v>7217984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 10274-2024 artfynd.xlsx
+++ b/artfynd/A 10274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118899285</v>
+        <v>118899277</v>
       </c>
       <c r="B2" t="n">
-        <v>90779</v>
+        <v>90016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>256703</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728146</v>
+        <v>728134</v>
       </c>
       <c r="R2" t="n">
-        <v>7217994</v>
+        <v>7217984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118897056</v>
+        <v>118899285</v>
       </c>
       <c r="B3" t="n">
-        <v>91780</v>
+        <v>90779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>71</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727904</v>
+        <v>728146</v>
       </c>
       <c r="R3" t="n">
-        <v>7217822</v>
+        <v>7217994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118897773</v>
+        <v>118897056</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>91780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727890</v>
+        <v>727904</v>
       </c>
       <c r="R4" t="n">
-        <v>7217789</v>
+        <v>7217822</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118897464</v>
+        <v>118897773</v>
       </c>
       <c r="B5" t="n">
-        <v>90756</v>
+        <v>91259</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727878</v>
+        <v>727890</v>
       </c>
       <c r="R5" t="n">
-        <v>7217756</v>
+        <v>7217789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118899277</v>
+        <v>118897464</v>
       </c>
       <c r="B6" t="n">
-        <v>90016</v>
+        <v>90756</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>256703</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728134</v>
+        <v>727878</v>
       </c>
       <c r="R6" t="n">
-        <v>7217984</v>
+        <v>7217756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1232,1686 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118996611</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>728016</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7217866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118997596</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>728141</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7217957</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118997618</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>728136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7217987</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118998051</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91414</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnforsen (Kvarnforsen), Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>728220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7218012</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118997552</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90533</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>728141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7217962</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118997418</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91414</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>728137</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7217913</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118997863</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästskomyran (Hästskomyran), Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>728157</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7218028</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118996583</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>727985</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7217859</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118996733</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>728051</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7217850</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118996290</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91414</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>727882</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7217793</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118996601</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91800</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>727979</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7217848</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118996435</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>727917</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7217786</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118996477</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>727946</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7217797</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118996199</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>727912</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7217836</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118997486</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Överstängena (Överstängena), Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>728152</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7217953</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10274-2024 artfynd.xlsx
+++ b/artfynd/A 10274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4724,6 +4724,118 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120461072</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Pelikan, Svansele, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>728083</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7217898</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
